--- a/data/600418_江淮汽车_财务数据.xlsx
+++ b/data/600418_江淮汽车_财务数据.xlsx
@@ -11157,7 +11157,7 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>归属于少数股东的综合收益总额</t>
+          <t>minority_common_profit_total</t>
         </is>
       </c>
       <c r="B27" s="3" t="n">
@@ -18992,7 +18992,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC11"/>
+  <dimension ref="A1:AA11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -19022,8 +19022,6 @@
     <col width="16" customWidth="1" min="25" max="25"/>
     <col width="16" customWidth="1" min="26" max="26"/>
     <col width="16" customWidth="1" min="27" max="27"/>
-    <col width="16" customWidth="1" min="28" max="28"/>
-    <col width="16" customWidth="1" min="29" max="29"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -19070,22 +19068,22 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>财务费用率(%)</t>
+          <t>资产负债率(%)</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>资产负债率(%)</t>
+          <t>流动比率</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>流动比率</t>
+          <t>速动比率</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>速动比率</t>
+          <t>产权比率(%)</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
@@ -19095,75 +19093,65 @@
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>应收账款周转天数(天)</t>
+          <t>存货周转率(次)</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>存货周转率(次)</t>
+          <t>总资产周转率(次)</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>存货周转天数(天)</t>
+          <t>流动资产周转率(次)</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>总资产周转率(次)</t>
+          <t>固定资产周转率(次)</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>流动资产周转率(次)</t>
+          <t>营收同比(%)</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>固定资产周转率(次)</t>
+          <t>净利润同比(%)</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>营收同比(%)</t>
+          <t>总资产增长率(%)</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>净利润同比(%)</t>
+          <t>经营现金流/净利润</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>总资产增长率(%)</t>
+          <t>自由现金流(元)</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>经营现金流/净利润</t>
+          <t>现金收入比</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>自由现金流(元)</t>
+          <t>现金流组合</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>现金收入比</t>
+          <t>Altman Z-score</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>现金流组合</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>Altman Z-score</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>Z-score判定</t>
         </is>
@@ -19197,58 +19185,52 @@
         <v>6.354737327434888</v>
       </c>
       <c r="I2" s="4" t="inlineStr"/>
-      <c r="J2" s="6" t="n">
-        <v>-0.2038958208743309</v>
+      <c r="J2" s="3" t="n">
+        <v>68.56852585593822</v>
       </c>
       <c r="K2" s="3" t="n">
-        <v>68.56852585593822</v>
-      </c>
-      <c r="L2" s="3" t="n">
         <v>1.028209537667835</v>
       </c>
-      <c r="M2" s="6" t="n">
+      <c r="L2" s="6" t="n">
         <v>0.9343210529796946</v>
+      </c>
+      <c r="M2" s="3" t="n">
+        <v>218.1524339000581</v>
       </c>
       <c r="N2" s="3" t="n">
         <v>10.4313507077345</v>
       </c>
       <c r="O2" s="3" t="n">
-        <v>34.51135045560994</v>
+        <v>19.5169338035435</v>
       </c>
       <c r="P2" s="3" t="n">
-        <v>19.5169338035435</v>
+        <v>1.066556065454028</v>
       </c>
       <c r="Q2" s="3" t="n">
-        <v>18.44552036829875</v>
-      </c>
-      <c r="R2" s="3" t="n">
-        <v>1.066556065454028</v>
-      </c>
-      <c r="S2" s="3" t="n">
         <v>1.688287824814898</v>
       </c>
+      <c r="R2" s="4" t="inlineStr"/>
+      <c r="S2" s="4" t="inlineStr"/>
       <c r="T2" s="4" t="inlineStr"/>
       <c r="U2" s="4" t="inlineStr"/>
-      <c r="V2" s="4" t="inlineStr"/>
-      <c r="W2" s="4" t="inlineStr"/>
+      <c r="V2" s="6" t="n">
+        <v>-0.2881581749507562</v>
+      </c>
+      <c r="W2" s="3" t="n">
+        <v>-1150000000</v>
+      </c>
       <c r="X2" s="6" t="n">
-        <v>-0.2881581749507562</v>
-      </c>
-      <c r="Y2" s="3" t="n">
-        <v>-1150000000</v>
-      </c>
-      <c r="Z2" s="6" t="n">
         <v>0.7691859734616515</v>
       </c>
+      <c r="Y2" s="4" t="inlineStr">
+        <is>
+          <t>−/−/+</t>
+        </is>
+      </c>
+      <c r="Z2" s="3" t="n">
+        <v>1.643792108396918</v>
+      </c>
       <c r="AA2" s="4" t="inlineStr">
-        <is>
-          <t>−/−/+</t>
-        </is>
-      </c>
-      <c r="AB2" s="3" t="n">
-        <v>1.643792108396918</v>
-      </c>
-      <c r="AC2" s="4" t="inlineStr">
         <is>
           <t>危险区</t>
         </is>
@@ -19284,64 +19266,58 @@
       <c r="I3" s="3" t="n">
         <v>2.778656510284557</v>
       </c>
-      <c r="J3" s="6" t="n">
-        <v>-0.07823652482290289</v>
-      </c>
-      <c r="K3" s="3" t="n">
+      <c r="J3" s="3" t="n">
         <v>65.74028308245337</v>
       </c>
+      <c r="K3" s="6" t="n">
+        <v>0.9412566116364802</v>
+      </c>
       <c r="L3" s="6" t="n">
-        <v>0.9412566116364802</v>
-      </c>
-      <c r="M3" s="6" t="n">
         <v>0.8776246193300208</v>
+      </c>
+      <c r="M3" s="3" t="n">
+        <v>191.8879926552561</v>
       </c>
       <c r="N3" s="3" t="n">
         <v>10.80017374244149</v>
       </c>
       <c r="O3" s="3" t="n">
-        <v>33.3327970998565</v>
+        <v>22.52695022044725</v>
       </c>
       <c r="P3" s="3" t="n">
-        <v>22.52695022044725</v>
+        <v>1.048731728247106</v>
       </c>
       <c r="Q3" s="3" t="n">
-        <v>15.98085832645181</v>
-      </c>
-      <c r="R3" s="3" t="n">
-        <v>1.048731728247106</v>
-      </c>
+        <v>1.800853433062055</v>
+      </c>
+      <c r="R3" s="4" t="inlineStr"/>
       <c r="S3" s="3" t="n">
-        <v>1.800853433062055</v>
-      </c>
-      <c r="T3" s="4" t="inlineStr"/>
+        <v>-6.371367256680427</v>
+      </c>
+      <c r="T3" s="3" t="n">
+        <v>-80.45990050271244</v>
+      </c>
       <c r="U3" s="3" t="n">
-        <v>-6.371367256680427</v>
+        <v>-9.560093467438788</v>
       </c>
       <c r="V3" s="3" t="n">
-        <v>-80.45990050271244</v>
+        <v>-28.07410649445568</v>
       </c>
       <c r="W3" s="3" t="n">
-        <v>-9.560093467438788</v>
-      </c>
-      <c r="X3" s="3" t="n">
-        <v>-28.07410649445568</v>
-      </c>
-      <c r="Y3" s="3" t="n">
         <v>-8270000000</v>
       </c>
-      <c r="Z3" s="6" t="n">
+      <c r="X3" s="6" t="n">
         <v>0.5697694907703559</v>
       </c>
+      <c r="Y3" s="4" t="inlineStr">
+        <is>
+          <t>−/−/+</t>
+        </is>
+      </c>
+      <c r="Z3" s="3" t="n">
+        <v>1.619822141219365</v>
+      </c>
       <c r="AA3" s="4" t="inlineStr">
-        <is>
-          <t>−/−/+</t>
-        </is>
-      </c>
-      <c r="AB3" s="3" t="n">
-        <v>1.619822141219365</v>
-      </c>
-      <c r="AC3" s="4" t="inlineStr">
         <is>
           <t>危险区</t>
         </is>
@@ -19377,64 +19353,58 @@
       <c r="I4" s="3" t="n">
         <v>2.875788397872669</v>
       </c>
-      <c r="J4" s="6" t="n">
-        <v>0.01335809994079995</v>
-      </c>
-      <c r="K4" s="3" t="n">
+      <c r="J4" s="3" t="n">
         <v>71.10039585614419</v>
       </c>
+      <c r="K4" s="6" t="n">
+        <v>0.9124908155767818</v>
+      </c>
       <c r="L4" s="6" t="n">
-        <v>0.9124908155767818</v>
-      </c>
-      <c r="M4" s="6" t="n">
         <v>0.8350477590007348</v>
+      </c>
+      <c r="M4" s="3" t="n">
+        <v>246.0255009107468</v>
       </c>
       <c r="N4" s="3" t="n">
         <v>11.54719858839788</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>31.17639289253346</v>
+        <v>28.08471963151515</v>
       </c>
       <c r="P4" s="3" t="n">
-        <v>28.08471963151515</v>
+        <v>1.088927359763266</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>12.81835833589834</v>
-      </c>
-      <c r="R4" s="3" t="n">
-        <v>1.088927359763266</v>
-      </c>
+        <v>2.072990708345886</v>
+      </c>
+      <c r="R4" s="4" t="inlineStr"/>
       <c r="S4" s="3" t="n">
-        <v>2.072990708345886</v>
-      </c>
-      <c r="T4" s="4" t="inlineStr"/>
+        <v>1.923967757537219</v>
+      </c>
+      <c r="T4" s="3" t="n">
+        <v>-698.5687234926157</v>
+      </c>
       <c r="U4" s="3" t="n">
-        <v>1.923967757537219</v>
+        <v>6.699618063356549</v>
       </c>
       <c r="V4" s="3" t="n">
-        <v>-698.5687234926157</v>
+        <v>2.431332988669896</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>6.699618063356549</v>
-      </c>
-      <c r="X4" s="3" t="n">
-        <v>2.431332988669896</v>
-      </c>
-      <c r="Y4" s="3" t="n">
         <v>-4271000000</v>
       </c>
-      <c r="Z4" s="6" t="n">
+      <c r="X4" s="6" t="n">
         <v>0.5464772418422538</v>
       </c>
+      <c r="Y4" s="4" t="inlineStr">
+        <is>
+          <t>−/−/+</t>
+        </is>
+      </c>
+      <c r="Z4" s="3" t="n">
+        <v>1.330964086327975</v>
+      </c>
       <c r="AA4" s="4" t="inlineStr">
-        <is>
-          <t>−/−/+</t>
-        </is>
-      </c>
-      <c r="AB4" s="3" t="n">
-        <v>1.330964086327975</v>
-      </c>
-      <c r="AC4" s="4" t="inlineStr">
         <is>
           <t>危险区</t>
         </is>
@@ -19470,64 +19440,58 @@
       <c r="I5" s="3" t="n">
         <v>2.502019037421893</v>
       </c>
-      <c r="J5" s="6" t="n">
-        <v>0.6690499821060569</v>
-      </c>
-      <c r="K5" s="3" t="n">
+      <c r="J5" s="3" t="n">
         <v>68.749287424467</v>
       </c>
+      <c r="K5" s="6" t="n">
+        <v>0.8570305745500275</v>
+      </c>
       <c r="L5" s="6" t="n">
-        <v>0.8570305745500275</v>
-      </c>
-      <c r="M5" s="6" t="n">
         <v>0.7485262909691111</v>
+      </c>
+      <c r="M5" s="3" t="n">
+        <v>220.0087565674256</v>
       </c>
       <c r="N5" s="3" t="n">
         <v>12.04586515249777</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>29.88577370263457</v>
+        <v>19.81589776871226</v>
       </c>
       <c r="P5" s="3" t="n">
-        <v>19.81589776871226</v>
+        <v>1.035305891953321</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>18.16723139177734</v>
-      </c>
-      <c r="R5" s="3" t="n">
-        <v>1.035305891953321</v>
-      </c>
+        <v>2.027442595555031</v>
+      </c>
+      <c r="R5" s="4" t="inlineStr"/>
       <c r="S5" s="3" t="n">
-        <v>2.027442595555031</v>
-      </c>
-      <c r="T5" s="4" t="inlineStr"/>
+        <v>-5.601129850097463</v>
+      </c>
+      <c r="T5" s="3" t="n">
+        <v>112.0917392755286</v>
+      </c>
       <c r="U5" s="3" t="n">
-        <v>-5.601129850097463</v>
+        <v>-7.658131895898257</v>
       </c>
       <c r="V5" s="3" t="n">
-        <v>112.0917392755286</v>
+        <v>1.315654254131748</v>
       </c>
       <c r="W5" s="3" t="n">
-        <v>-7.658131895898257</v>
-      </c>
-      <c r="X5" s="3" t="n">
-        <v>1.315654254131748</v>
-      </c>
-      <c r="Y5" s="3" t="n">
         <v>4999999.99999997</v>
       </c>
-      <c r="Z5" s="6" t="n">
+      <c r="X5" s="6" t="n">
         <v>0.7110343221882418</v>
       </c>
+      <c r="Y5" s="4" t="inlineStr">
+        <is>
+          <t>+/+/−</t>
+        </is>
+      </c>
+      <c r="Z5" s="3" t="n">
+        <v>1.473284127715738</v>
+      </c>
       <c r="AA5" s="4" t="inlineStr">
-        <is>
-          <t>+/+/−</t>
-        </is>
-      </c>
-      <c r="AB5" s="3" t="n">
-        <v>1.473284127715738</v>
-      </c>
-      <c r="AC5" s="4" t="inlineStr">
         <is>
           <t>危险区</t>
         </is>
@@ -19563,64 +19527,58 @@
       <c r="I6" s="3" t="n">
         <v>3.914688673838286</v>
       </c>
-      <c r="J6" s="6" t="n">
-        <v>0.8545491736884615</v>
-      </c>
-      <c r="K6" s="3" t="n">
+      <c r="J6" s="3" t="n">
         <v>66.96583327397488</v>
       </c>
+      <c r="K6" s="6" t="n">
+        <v>0.9513560644302694</v>
+      </c>
       <c r="L6" s="6" t="n">
-        <v>0.9513560644302694</v>
-      </c>
-      <c r="M6" s="6" t="n">
         <v>0.8640264329310265</v>
+      </c>
+      <c r="M6" s="3" t="n">
+        <v>202.7023142158977</v>
       </c>
       <c r="N6" s="3" t="n">
         <v>14.77687360460583</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>24.36239286013727</v>
-      </c>
-      <c r="P6" s="3" t="n">
         <v>19.18994771043311</v>
       </c>
+      <c r="P6" s="6" t="n">
+        <v>0.9963887810670915</v>
+      </c>
       <c r="Q6" s="3" t="n">
-        <v>18.75982183131623</v>
-      </c>
-      <c r="R6" s="6" t="n">
-        <v>0.9963887810670915</v>
-      </c>
+        <v>2.013717677564117</v>
+      </c>
+      <c r="R6" s="4" t="inlineStr"/>
       <c r="S6" s="3" t="n">
-        <v>2.013717677564117</v>
-      </c>
-      <c r="T6" s="4" t="inlineStr"/>
+        <v>-9.421967178263674</v>
+      </c>
+      <c r="T6" s="3" t="n">
+        <v>45.23409048869874</v>
+      </c>
       <c r="U6" s="3" t="n">
-        <v>-9.421967178263674</v>
+        <v>-3.963060084368943</v>
       </c>
       <c r="V6" s="3" t="n">
-        <v>45.23409048869874</v>
+        <v>-5.335103159115972</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>-3.963060084368943</v>
-      </c>
-      <c r="X6" s="3" t="n">
-        <v>-5.335103159115972</v>
-      </c>
-      <c r="Y6" s="3" t="n">
         <v>-1568000000</v>
       </c>
-      <c r="Z6" s="6" t="n">
+      <c r="X6" s="6" t="n">
         <v>0.8149281816171501</v>
       </c>
+      <c r="Y6" s="4" t="inlineStr">
+        <is>
+          <t>−/+/−</t>
+        </is>
+      </c>
+      <c r="Z6" s="3" t="n">
+        <v>1.517853637505857</v>
+      </c>
       <c r="AA6" s="4" t="inlineStr">
-        <is>
-          <t>−/+/−</t>
-        </is>
-      </c>
-      <c r="AB6" s="3" t="n">
-        <v>1.517853637505857</v>
-      </c>
-      <c r="AC6" s="4" t="inlineStr">
         <is>
           <t>危险区</t>
         </is>
@@ -19656,64 +19614,58 @@
       <c r="I7" s="3" t="n">
         <v>3.417034700431718</v>
       </c>
-      <c r="J7" s="6" t="n">
-        <v>0.5613726775265049</v>
+      <c r="J7" s="3" t="n">
+        <v>65.78175544533103</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>65.78175544533103</v>
+        <v>1.137108325872874</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>1.137108325872874</v>
+        <v>1.019919427036705</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>1.019919427036705</v>
+        <v>192.2417596268986</v>
       </c>
       <c r="N7" s="3" t="n">
         <v>16.98564777892714</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>21.19436389388846</v>
-      </c>
-      <c r="P7" s="3" t="n">
         <v>18.6870254432338</v>
       </c>
+      <c r="P7" s="6" t="n">
+        <v>0.9089136509681648</v>
+      </c>
       <c r="Q7" s="3" t="n">
-        <v>19.26470326128597</v>
-      </c>
-      <c r="R7" s="6" t="n">
-        <v>0.9089136509681648</v>
-      </c>
+        <v>1.743335549339316</v>
+      </c>
+      <c r="R7" s="4" t="inlineStr"/>
       <c r="S7" s="3" t="n">
-        <v>1.743335549339316</v>
-      </c>
-      <c r="T7" s="4" t="inlineStr"/>
+        <v>-6.110670295720108</v>
+      </c>
+      <c r="T7" s="3" t="n">
+        <v>-94.77292064280519</v>
+      </c>
       <c r="U7" s="3" t="n">
-        <v>-6.110670295720108</v>
+        <v>10.0980601657288</v>
       </c>
       <c r="V7" s="3" t="n">
-        <v>-94.77292064280519</v>
+        <v>132.2801783161036</v>
       </c>
       <c r="W7" s="3" t="n">
-        <v>10.0980601657288</v>
+        <v>1057000000</v>
       </c>
       <c r="X7" s="3" t="n">
-        <v>132.2801783161036</v>
-      </c>
-      <c r="Y7" s="3" t="n">
-        <v>1057000000</v>
+        <v>1.186342271835899</v>
+      </c>
+      <c r="Y7" s="4" t="inlineStr">
+        <is>
+          <t>+/−/+</t>
+        </is>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>1.186342271835899</v>
+        <v>1.478592431128875</v>
       </c>
       <c r="AA7" s="4" t="inlineStr">
-        <is>
-          <t>+/−/+</t>
-        </is>
-      </c>
-      <c r="AB7" s="3" t="n">
-        <v>1.478592431128875</v>
-      </c>
-      <c r="AC7" s="4" t="inlineStr">
         <is>
           <t>危险区</t>
         </is>
@@ -19749,64 +19701,58 @@
       <c r="I8" s="3" t="n">
         <v>4.211503412825454</v>
       </c>
-      <c r="J8" s="6" t="n">
-        <v>0.04472949325609632</v>
-      </c>
-      <c r="K8" s="3" t="n">
+      <c r="J8" s="3" t="n">
         <v>70.12085041310027</v>
       </c>
+      <c r="K8" s="6" t="n">
+        <v>0.9607332848559071</v>
+      </c>
       <c r="L8" s="6" t="n">
-        <v>0.9607332848559071</v>
-      </c>
-      <c r="M8" s="6" t="n">
         <v>0.8310689272455891</v>
+      </c>
+      <c r="M8" s="3" t="n">
+        <v>234.6982298997654</v>
       </c>
       <c r="N8" s="3" t="n">
         <v>13.8763018623232</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>25.94351172032864</v>
-      </c>
-      <c r="P8" s="3" t="n">
         <v>12.8033027933966</v>
       </c>
+      <c r="P8" s="6" t="n">
+        <v>0.7810273377614416</v>
+      </c>
       <c r="Q8" s="3" t="n">
-        <v>28.11774475767867</v>
-      </c>
-      <c r="R8" s="6" t="n">
-        <v>0.7810273377614416</v>
-      </c>
+        <v>1.445161917313191</v>
+      </c>
+      <c r="R8" s="4" t="inlineStr"/>
       <c r="S8" s="3" t="n">
-        <v>1.445161917313191</v>
-      </c>
-      <c r="T8" s="4" t="inlineStr"/>
+        <v>-9.247753281579575</v>
+      </c>
+      <c r="T8" s="3" t="n">
+        <v>-13345.09665472225</v>
+      </c>
       <c r="U8" s="3" t="n">
-        <v>-9.247753281579575</v>
-      </c>
-      <c r="V8" s="3" t="n">
-        <v>-13345.09665472225</v>
+        <v>1.537632089713177</v>
+      </c>
+      <c r="V8" s="6" t="n">
+        <v>-0.886391802763993</v>
       </c>
       <c r="W8" s="3" t="n">
-        <v>1.537632089713177</v>
+        <v>1128000000</v>
       </c>
       <c r="X8" s="6" t="n">
-        <v>-0.886391802763993</v>
-      </c>
-      <c r="Y8" s="3" t="n">
-        <v>1128000000</v>
-      </c>
-      <c r="Z8" s="6" t="n">
         <v>0.8491924078207701</v>
       </c>
+      <c r="Y8" s="4" t="inlineStr">
+        <is>
+          <t>+/+/−</t>
+        </is>
+      </c>
+      <c r="Z8" s="3" t="n">
+        <v>1.06172514068921</v>
+      </c>
       <c r="AA8" s="4" t="inlineStr">
-        <is>
-          <t>+/+/−</t>
-        </is>
-      </c>
-      <c r="AB8" s="3" t="n">
-        <v>1.06172514068921</v>
-      </c>
-      <c r="AC8" s="4" t="inlineStr">
         <is>
           <t>危险区</t>
         </is>
@@ -19842,64 +19788,58 @@
       <c r="I9" s="3" t="n">
         <v>3.548249235663988</v>
       </c>
-      <c r="J9" s="6" t="n">
-        <v>0.7826191084539398</v>
+      <c r="J9" s="3" t="n">
+        <v>69.00821144470103</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>69.00821144470103</v>
-      </c>
-      <c r="L9" s="3" t="n">
         <v>1.076558240280838</v>
       </c>
-      <c r="M9" s="6" t="n">
+      <c r="L9" s="6" t="n">
         <v>0.899316577659932</v>
+      </c>
+      <c r="M9" s="3" t="n">
+        <v>222.6661146760505</v>
       </c>
       <c r="N9" s="3" t="n">
         <v>14.85631749442645</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>24.23211540377076</v>
-      </c>
-      <c r="P9" s="3" t="n">
         <v>11.25838838858618</v>
       </c>
+      <c r="P9" s="6" t="n">
+        <v>0.9577367506822807</v>
+      </c>
       <c r="Q9" s="3" t="n">
-        <v>31.97615747250025</v>
-      </c>
-      <c r="R9" s="6" t="n">
-        <v>0.9577367506822807</v>
-      </c>
+        <v>1.666618224388652</v>
+      </c>
+      <c r="R9" s="4" t="inlineStr"/>
       <c r="S9" s="3" t="n">
-        <v>1.666618224388652</v>
-      </c>
-      <c r="T9" s="4" t="inlineStr"/>
-      <c r="U9" s="3" t="n">
         <v>23.14224411582882</v>
       </c>
+      <c r="T9" s="3" t="n">
+        <v>95.84709470415385</v>
+      </c>
+      <c r="U9" s="6" t="n">
+        <v>-0.6775269205445702</v>
+      </c>
       <c r="V9" s="3" t="n">
-        <v>95.84709470415385</v>
-      </c>
-      <c r="W9" s="6" t="n">
-        <v>-0.6775269205445702</v>
-      </c>
-      <c r="X9" s="3" t="n">
         <v>-47.34413591025443</v>
       </c>
-      <c r="Y9" s="3" t="n">
+      <c r="W9" s="3" t="n">
         <v>1336000000</v>
       </c>
-      <c r="Z9" s="6" t="n">
+      <c r="X9" s="6" t="n">
         <v>0.8924049479047071</v>
       </c>
+      <c r="Y9" s="4" t="inlineStr">
+        <is>
+          <t>+/+/−</t>
+        </is>
+      </c>
+      <c r="Z9" s="3" t="n">
+        <v>1.441108202827579</v>
+      </c>
       <c r="AA9" s="4" t="inlineStr">
-        <is>
-          <t>+/+/−</t>
-        </is>
-      </c>
-      <c r="AB9" s="3" t="n">
-        <v>1.441108202827579</v>
-      </c>
-      <c r="AC9" s="4" t="inlineStr">
         <is>
           <t>危险区</t>
         </is>
@@ -19935,64 +19875,58 @@
       <c r="I10" s="3" t="n">
         <v>4.185897733103251</v>
       </c>
-      <c r="J10" s="6" t="n">
-        <v>0.0967868319013688</v>
-      </c>
-      <c r="K10" s="3" t="n">
+      <c r="J10" s="3" t="n">
         <v>74.67655508241478</v>
       </c>
+      <c r="K10" s="6" t="n">
+        <v>0.9128127369219106</v>
+      </c>
       <c r="L10" s="6" t="n">
-        <v>0.9128127369219106</v>
-      </c>
-      <c r="M10" s="6" t="n">
         <v>0.7948379866170023</v>
+      </c>
+      <c r="M10" s="3" t="n">
+        <v>294.890980770778</v>
       </c>
       <c r="N10" s="3" t="n">
         <v>13.86075097276946</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>25.97261870639249</v>
-      </c>
-      <c r="P10" s="3" t="n">
         <v>10.35756049584625</v>
       </c>
+      <c r="P10" s="6" t="n">
+        <v>0.8788333628412541</v>
+      </c>
       <c r="Q10" s="3" t="n">
-        <v>34.75721914869558</v>
-      </c>
-      <c r="R10" s="6" t="n">
-        <v>0.8788333628412541</v>
-      </c>
+        <v>1.490326857543835</v>
+      </c>
+      <c r="R10" s="4" t="inlineStr"/>
       <c r="S10" s="3" t="n">
-        <v>1.490326857543835</v>
-      </c>
-      <c r="T10" s="4" t="inlineStr"/>
+        <v>-6.284926430146716</v>
+      </c>
+      <c r="T10" s="3" t="n">
+        <v>-2679.191047264384</v>
+      </c>
       <c r="U10" s="3" t="n">
-        <v>-6.284926430146716</v>
+        <v>4.954665982379608</v>
       </c>
       <c r="V10" s="3" t="n">
-        <v>-2679.191047264384</v>
+        <v>-1.359908312586602</v>
       </c>
       <c r="W10" s="3" t="n">
-        <v>4.954665982379608</v>
-      </c>
-      <c r="X10" s="3" t="n">
-        <v>-1.359908312586602</v>
-      </c>
-      <c r="Y10" s="3" t="n">
         <v>637000000.0000002</v>
       </c>
+      <c r="X10" s="6" t="n">
+        <v>0.8864587303534798</v>
+      </c>
+      <c r="Y10" s="4" t="inlineStr">
+        <is>
+          <t>+/−/+</t>
+        </is>
+      </c>
       <c r="Z10" s="6" t="n">
-        <v>0.8864587303534798</v>
+        <v>0.9616696220207182</v>
       </c>
       <c r="AA10" s="4" t="inlineStr">
-        <is>
-          <t>+/−/+</t>
-        </is>
-      </c>
-      <c r="AB10" s="6" t="n">
-        <v>0.9616696220207182</v>
-      </c>
-      <c r="AC10" s="4" t="inlineStr">
         <is>
           <t>危险区</t>
         </is>
@@ -20028,64 +19962,58 @@
       <c r="I11" s="3" t="n">
         <v>3.892351238699869</v>
       </c>
-      <c r="J11" s="6" t="n">
-        <v>-0.3473419544919574</v>
-      </c>
-      <c r="K11" s="3" t="n">
+      <c r="J11" s="3" t="n">
         <v>79.07036163522012</v>
       </c>
+      <c r="K11" s="6" t="n">
+        <v>0.8025869859918663</v>
+      </c>
       <c r="L11" s="6" t="n">
-        <v>0.8025869859918663</v>
-      </c>
-      <c r="M11" s="6" t="n">
         <v>0.7174932218707637</v>
+      </c>
+      <c r="M11" s="3" t="n">
+        <v>377.8268219383922</v>
       </c>
       <c r="N11" s="3" t="n">
         <v>15.07483647471619</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>23.88085606127795</v>
-      </c>
-      <c r="P11" s="3" t="n">
         <v>14.59421094532767</v>
       </c>
+      <c r="P11" s="6" t="n">
+        <v>0.9298770690879443</v>
+      </c>
       <c r="Q11" s="3" t="n">
-        <v>24.66731509833725</v>
-      </c>
-      <c r="R11" s="6" t="n">
-        <v>0.9298770690879443</v>
-      </c>
+        <v>1.656593151008733</v>
+      </c>
+      <c r="R11" s="4" t="inlineStr"/>
       <c r="S11" s="3" t="n">
-        <v>1.656593151008733</v>
-      </c>
-      <c r="T11" s="4" t="inlineStr"/>
+        <v>10.35198076372143</v>
+      </c>
+      <c r="T11" s="3" t="n">
+        <v>11.13617441878554</v>
+      </c>
       <c r="U11" s="3" t="n">
-        <v>10.35198076372143</v>
+        <v>3.66536949124916</v>
       </c>
       <c r="V11" s="3" t="n">
-        <v>11.13617441878554</v>
+        <v>-1.916438486208548</v>
       </c>
       <c r="W11" s="3" t="n">
-        <v>3.66536949124916</v>
-      </c>
-      <c r="X11" s="3" t="n">
-        <v>-1.916438486208548</v>
-      </c>
-      <c r="Y11" s="3" t="n">
         <v>1673000000</v>
       </c>
+      <c r="X11" s="6" t="n">
+        <v>0.9205021292009335</v>
+      </c>
+      <c r="Y11" s="4" t="inlineStr">
+        <is>
+          <t>+/+/−</t>
+        </is>
+      </c>
       <c r="Z11" s="6" t="n">
-        <v>0.9205021292009335</v>
+        <v>0.8385587714886311</v>
       </c>
       <c r="AA11" s="4" t="inlineStr">
-        <is>
-          <t>+/+/−</t>
-        </is>
-      </c>
-      <c r="AB11" s="6" t="n">
-        <v>0.8385587714886311</v>
-      </c>
-      <c r="AC11" s="4" t="inlineStr">
         <is>
           <t>危险区</t>
         </is>

--- a/data/600418_江淮汽车_财务数据.xlsx
+++ b/data/600418_江淮汽车_财务数据.xlsx
@@ -13,6 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="财务分析指标" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据质量校验" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="合并报表" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="财务指标表" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -39722,4 +39723,2123 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:P40"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>毛利率</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>营业利润率</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>净利润率</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>净资产收益率</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>存货周转率</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>总资产周转率</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>应收账款周转率</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>流动比率</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>速动比率</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>利息保障倍数</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>资产负债率</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>货币资金占比</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>营业收入增长率</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>营业利润增长率</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>净利润增长率</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2016Q1</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>-0.04189361397840208</v>
+      </c>
+      <c r="C2" t="n">
+        <v>-0.03721589913007799</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.01894935392453205</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.02491008084966156</v>
+      </c>
+      <c r="F2" t="n">
+        <v>5.71181215736033</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.308015535935367</v>
+      </c>
+      <c r="H2" t="n">
+        <v>4.4298989425178</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.8902589395807645</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.793865598027127</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.7743487675247698</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.3315106843682334</v>
+      </c>
+      <c r="N2" t="n">
+        <v>-0.7214569179316832</v>
+      </c>
+      <c r="O2" t="n">
+        <v>-0.7945121140154512</v>
+      </c>
+      <c r="P2" t="n">
+        <v>-0.77189706996788</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2016Q2</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>-0.04655554066613776</v>
+      </c>
+      <c r="C3" t="n">
+        <v>-0.04222593197833024</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.02266635722584634</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.0665190698888441</v>
+      </c>
+      <c r="F3" t="n">
+        <v>13.08642295818526</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.5796685845610798</v>
+      </c>
+      <c r="H3" t="n">
+        <v>7.92977217999399</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.8832073281676444</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.8130313392100887</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.7713756286949616</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.3414365128386129</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.8049720112714116</v>
+      </c>
+      <c r="O3" t="n">
+        <v>1.047958726036476</v>
+      </c>
+      <c r="P3" t="n">
+        <v>1.15902560863391</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2016Q3</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>-0.0474700673616284</v>
+      </c>
+      <c r="C4" t="n">
+        <v>-0.04276833323647599</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.02204508801981398</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.07382316411865632</v>
+      </c>
+      <c r="F4" t="n">
+        <v>20.8400296897365</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.7882880789669323</v>
+      </c>
+      <c r="H4" t="n">
+        <v>9.456817590195932</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1.034129067708651</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.94612003174797</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.7060047851543504</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.3558715400027233</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.4448458258588361</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.4634051839844224</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0.4052435990816581</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2017年报</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>-0.01459347487577989</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.004055901227454292</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.004829186851720279</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.03162073766738661</v>
+      </c>
+      <c r="F5" t="n">
+        <v>26.9896640394912</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1.024743598556699</v>
+      </c>
+      <c r="H5" t="n">
+        <v>12.67798029536438</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.9412566116364802</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.8589517550889566</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1.697011687801175</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.6574028308245338</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.2484834868568861</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.2889151402703782</v>
+      </c>
+      <c r="O5" t="n">
+        <v>-1.122233253061367</v>
+      </c>
+      <c r="P5" t="n">
+        <v>-0.7176508416395322</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2017Q1</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0.006911903298939093</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.02084613295760719</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.01870792645740986</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.01957915230059044</v>
+      </c>
+      <c r="F6" t="n">
+        <v>5.515015169653496</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.2851705202212187</v>
+      </c>
+      <c r="H6" t="n">
+        <v>3.618435130095062</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1.038482213438735</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.9133913043478261</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.6951389696476333</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.305655696398806</v>
+      </c>
+      <c r="N6" t="n">
+        <v>-0.7211785152378982</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.4330599826851245</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0.08013460481801249</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2017Q2</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>-0.002803342951880561</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.01157088550907999</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.01229124805049781</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.02474260718326035</v>
+      </c>
+      <c r="F7" t="n">
+        <v>9.28810339996341</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.5078682727044189</v>
+      </c>
+      <c r="H7" t="n">
+        <v>6.381803701568133</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1.009688581314879</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.9141176470588235</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.6791083570730491</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.2884531409203385</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.8472888287307008</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.02535887988977392</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0.2136826209218605</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2017Q3</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>-0.01303940007431814</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.002419768333209273</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.003518472597803344</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.01594221822601217</v>
+      </c>
+      <c r="F8" t="n">
+        <v>15.74677181633501</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.7458173567295847</v>
+      </c>
+      <c r="H8" t="n">
+        <v>10.50282305740839</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1.013055585693103</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.9008354128241294</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1.407832922880898</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.6788936422550722</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.2822440594688466</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.4040594701665086</v>
+      </c>
+      <c r="O8" t="n">
+        <v>-0.7063752258904128</v>
+      </c>
+      <c r="P8" t="n">
+        <v>-0.5980762286164212</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2018年报</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>-0.03611002797256502</v>
+      </c>
+      <c r="C9" t="n">
+        <v>-0.03033377471635929</v>
+      </c>
+      <c r="D9" t="n">
+        <v>-0.02836035795052507</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-0.05930922701697473</v>
+      </c>
+      <c r="F9" t="n">
+        <v>22.75342476064884</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1.057792154502587</v>
+      </c>
+      <c r="H9" t="n">
+        <v>13.45106000979323</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.9124908155767818</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.8216752387950037</v>
+      </c>
+      <c r="K9" t="n">
+        <v>-2.607024042039243</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.7110039585614419</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.1970016002695191</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.4093854356214643</v>
+      </c>
+      <c r="O9" t="n">
+        <v>-18.66779889873119</v>
+      </c>
+      <c r="P9" t="n">
+        <v>-12.36023496941143</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2018Q1</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>-0.02508061669235828</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.01230803388455357</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.0112792615384568</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.01554505495415909</v>
+      </c>
+      <c r="F10" t="n">
+        <v>5.980258460276644</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.2592000028489391</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2.759295783223938</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.9434655641959511</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.8532335859828724</v>
+      </c>
+      <c r="K10" t="n">
+        <v>2.579787737747556</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.7025074373140672</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.2211103813313758</v>
+      </c>
+      <c r="N10" t="n">
+        <v>-0.7431944863286586</v>
+      </c>
+      <c r="O10" t="n">
+        <v>-1.104199724352223</v>
+      </c>
+      <c r="P10" t="n">
+        <v>-1.102134696546141</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2018Q2</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>-0.02723210507739737</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.002116728609421078</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.002015011674579819</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.01172489987734462</v>
+      </c>
+      <c r="F11" t="n">
+        <v>11.15658111262483</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.4740505871799896</v>
+      </c>
+      <c r="H11" t="n">
+        <v>4.994557840155888</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.9618747684327529</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.8680251945164876</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1.215520689162241</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.6859433923169367</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.232584642161535</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.8430866447735081</v>
+      </c>
+      <c r="O11" t="n">
+        <v>-0.6830270157502498</v>
+      </c>
+      <c r="P11" t="n">
+        <v>-0.6707372114904533</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2018Q3</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>-0.03158968743932467</v>
+      </c>
+      <c r="C12" t="n">
+        <v>-0.004282444793584296</v>
+      </c>
+      <c r="D12" t="n">
+        <v>-0.004568782871750156</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.003480246888120793</v>
+      </c>
+      <c r="F12" t="n">
+        <v>17.98838726947444</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.7585100895381852</v>
+      </c>
+      <c r="H12" t="n">
+        <v>7.501779118046665</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.9546759329203808</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.8532255627738329</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0.556213869891986</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.6854882820717803</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.1927672823663062</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.5323658438974346</v>
+      </c>
+      <c r="O12" t="n">
+        <v>-4.100195320674456</v>
+      </c>
+      <c r="P12" t="n">
+        <v>-4.474444793136728</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2019年报</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>-0.02021229495853794</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.004885052602408927</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.003632734730340067</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.007959380423439319</v>
+      </c>
+      <c r="F13" t="n">
+        <v>19.83626772941201</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1.034830092377201</v>
+      </c>
+      <c r="H13" t="n">
+        <v>11.05976930326979</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.8570305745500275</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0.7352432602373654</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1.537678397734085</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0.68749287424467</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.1876410899555353</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.3015301623657487</v>
+      </c>
+      <c r="O13" t="n">
+        <v>-2.484676070151274</v>
+      </c>
+      <c r="P13" t="n">
+        <v>-2.034873828792833</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2019Q1</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>-0.004801451633777987</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.003647268923333642</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0.00523600698385652</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.004995434130149161</v>
+      </c>
+      <c r="F14" t="n">
+        <v>6.256886686842553</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.3140589993645173</v>
+      </c>
+      <c r="H14" t="n">
+        <v>3.448432201223047</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.9564801360881738</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0.8632030336322075</v>
+      </c>
+      <c r="K14" t="n">
+        <v>1.452692711601431</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.7201727003689139</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.1903352657396522</v>
+      </c>
+      <c r="N14" t="n">
+        <v>-0.6905340156536235</v>
+      </c>
+      <c r="O14" t="n">
+        <v>-0.7689470801238036</v>
+      </c>
+      <c r="P14" t="n">
+        <v>-0.5539542037653891</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2019Q2</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>0.0005960333223827829</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.01085736090655867</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0.005893051973110742</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.009656491372670089</v>
+      </c>
+      <c r="F15" t="n">
+        <v>13.74981252389299</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.5464777622318474</v>
+      </c>
+      <c r="H15" t="n">
+        <v>4.500391705553796</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.8827561327561327</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0.8017184835366653</v>
+      </c>
+      <c r="K15" t="n">
+        <v>2.202106157422056</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0.7192861906590409</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0.1671550696226834</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0.8450981563163045</v>
+      </c>
+      <c r="O15" t="n">
+        <v>4.492574584503585</v>
+      </c>
+      <c r="P15" t="n">
+        <v>1.076631938075495</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2019Q3</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>-0.004933676275449717</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.009464471763668764</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0.006871074356289168</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.009364795300639002</v>
+      </c>
+      <c r="F16" t="n">
+        <v>18.6386212380798</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.7700839131672517</v>
+      </c>
+      <c r="H16" t="n">
+        <v>6.000801537016298</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.8631066272395199</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0.772273438858932</v>
+      </c>
+      <c r="K16" t="n">
+        <v>2.020312006274806</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0.7067816043144083</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0.1408340056902629</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0.3772899757142729</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0.2005976588341511</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0.6058677025902812</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2020年报</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>-0.04483202148911425</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.002951397124564701</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0.005824777908193194</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.01095176547304562</v>
+      </c>
+      <c r="F17" t="n">
+        <v>22.79142249082251</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.9601696607734125</v>
+      </c>
+      <c r="H17" t="n">
+        <v>10.38195810033935</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.9513560644302694</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0.8343352760313891</v>
+      </c>
+      <c r="K17" t="n">
+        <v>1.323220940236722</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0.6696583327397488</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0.1679844243417147</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0.1517682525468038</v>
+      </c>
+      <c r="O17" t="n">
+        <v>-0.6408330445043403</v>
+      </c>
+      <c r="P17" t="n">
+        <v>-0.02361786164455171</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2020Q1</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>-0.07073963999285926</v>
+      </c>
+      <c r="C18" t="n">
+        <v>-0.06335510656801806</v>
+      </c>
+      <c r="D18" t="n">
+        <v>-0.05189153849541921</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-0.02775118743304877</v>
+      </c>
+      <c r="F18" t="n">
+        <v>3.239708177396661</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.1741693429296696</v>
+      </c>
+      <c r="H18" t="n">
+        <v>2.021668740079671</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.8705636743215032</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0.733671339099314</v>
+      </c>
+      <c r="K18" t="n">
+        <v>-3.110526340695388</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0.7060641515265238</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0.1587673017064394</v>
+      </c>
+      <c r="N18" t="n">
+        <v>-0.8222634341891194</v>
+      </c>
+      <c r="O18" t="n">
+        <v>-4.815318167202831</v>
+      </c>
+      <c r="P18" t="n">
+        <v>-2.583412104665093</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2020Q2</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>-0.04448394949690138</v>
+      </c>
+      <c r="C19" t="n">
+        <v>-0.01318498820344335</v>
+      </c>
+      <c r="D19" t="n">
+        <v>-0.009283211866449042</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-0.0116224296306807</v>
+      </c>
+      <c r="F19" t="n">
+        <v>7.388922785909664</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.4313736552984166</v>
+      </c>
+      <c r="H19" t="n">
+        <v>4.421495060285682</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.9516261594458143</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0.8421588196156706</v>
+      </c>
+      <c r="K19" t="n">
+        <v>-0.4495680053717833</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0.7056423459591552</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0.1684630825624018</v>
+      </c>
+      <c r="N19" t="n">
+        <v>1.582005190088125</v>
+      </c>
+      <c r="O19" t="n">
+        <v>-0.4626525024310059</v>
+      </c>
+      <c r="P19" t="n">
+        <v>-0.5380884453449956</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2020Q3</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>-0.04193163670412381</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.004341483386866645</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0.007616162383974116</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.003292731362823603</v>
+      </c>
+      <c r="F20" t="n">
+        <v>13.4738889649276</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.6715412662422895</v>
+      </c>
+      <c r="H20" t="n">
+        <v>7.470815168266246</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.9726548567352277</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0.860420877422423</v>
+      </c>
+      <c r="K20" t="n">
+        <v>1.440515040697739</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0.6972738753647172</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0.1566868440534773</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0.5674615262105629</v>
+      </c>
+      <c r="O20" t="n">
+        <v>-1.516125465612369</v>
+      </c>
+      <c r="P20" t="n">
+        <v>-2.285981800910681</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2021年报</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>-0.05044323007522311</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.004076731471850285</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0.0003242815393405996</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.01418586046600702</v>
+      </c>
+      <c r="F21" t="n">
+        <v>17.0502607525449</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.8714033352823525</v>
+      </c>
+      <c r="H21" t="n">
+        <v>12.34111435218966</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1.137108325872874</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0.9868397493285587</v>
+      </c>
+      <c r="K21" t="n">
+        <v>1.45540719290819</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0.6578175544533104</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0.2242398102221264</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0.3052252096206365</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0.2256300936240987</v>
+      </c>
+      <c r="P21" t="n">
+        <v>-0.944426022080023</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2021Q1</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>-0.009647686367168617</v>
+      </c>
+      <c r="C22" t="n">
+        <v>0.01264783757882117</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0.01504810568300662</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0.01327893909279219</v>
+      </c>
+      <c r="F22" t="n">
+        <v>4.5383951570406</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.2490236893954738</v>
+      </c>
+      <c r="H22" t="n">
+        <v>3.664992669987449</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0.9906985645933014</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0.8703540669856459</v>
+      </c>
+      <c r="K22" t="n">
+        <v>2.614245203911193</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0.7037669428107675</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0.1676679525285103</v>
+      </c>
+      <c r="N22" t="n">
+        <v>-0.7095421809649617</v>
+      </c>
+      <c r="O22" t="n">
+        <v>-0.0988704200852234</v>
+      </c>
+      <c r="P22" t="n">
+        <v>12.47853462822034</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2021Q2</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>-0.02396717559395345</v>
+      </c>
+      <c r="C23" t="n">
+        <v>0.018798372459486</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0.01940109358984432</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0.03570893261651157</v>
+      </c>
+      <c r="F23" t="n">
+        <v>8.668084757099093</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.474310121678587</v>
+      </c>
+      <c r="H23" t="n">
+        <v>5.793188346532937</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.9986365938218222</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0.8718787737135288</v>
+      </c>
+      <c r="K23" t="n">
+        <v>3.214765033627239</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0.6953640973198688</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0.178810345562231</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0.9162112744828845</v>
+      </c>
+      <c r="O23" t="n">
+        <v>1.848048373827472</v>
+      </c>
+      <c r="P23" t="n">
+        <v>1.470516559179919</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2021Q3</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>-0.03818154537969631</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.0008547913517326134</v>
+      </c>
+      <c r="D24" t="n">
+        <v>0.004377247174631264</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.01456614887925234</v>
+      </c>
+      <c r="F24" t="n">
+        <v>12.67598693582356</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0.6708870634094631</v>
+      </c>
+      <c r="H24" t="n">
+        <v>8.352849426964795</v>
+      </c>
+      <c r="I24" t="n">
+        <v>1.015791085254363</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0.8971173614452561</v>
+      </c>
+      <c r="K24" t="n">
+        <v>1.088670254060862</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0.6863188535602329</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0.1840349305866547</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0.3727986646374457</v>
+      </c>
+      <c r="O24" t="n">
+        <v>-0.9375767009228492</v>
+      </c>
+      <c r="P24" t="n">
+        <v>-0.6902711154763287</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2022年报</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>-0.05353231532154834</v>
+      </c>
+      <c r="C25" t="n">
+        <v>-0.03811661689460016</v>
+      </c>
+      <c r="D25" t="n">
+        <v>-0.04732819833359069</v>
+      </c>
+      <c r="E25" t="n">
+        <v>-0.1177569601145961</v>
+      </c>
+      <c r="F25" t="n">
+        <v>13.46229631952731</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0.7955849252348409</v>
+      </c>
+      <c r="H25" t="n">
+        <v>10.57816634722029</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.9607332848559073</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0.8037046959317233</v>
+      </c>
+      <c r="K25" t="n">
+        <v>-2.824019816136949</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0.7012085041310027</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0.2700337701505852</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0.1877473613827665</v>
+      </c>
+      <c r="O25" t="n">
+        <v>-53.96369815819207</v>
+      </c>
+      <c r="P25" t="n">
+        <v>-13.8423048658334</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2022Q1</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>-0.04830128145164481</v>
+      </c>
+      <c r="C26" t="n">
+        <v>-0.02692948102858007</v>
+      </c>
+      <c r="D26" t="n">
+        <v>-0.03398712642012292</v>
+      </c>
+      <c r="E26" t="n">
+        <v>-0.02029367143986014</v>
+      </c>
+      <c r="F26" t="n">
+        <v>3.30788559455956</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0.2068740053554588</v>
+      </c>
+      <c r="H26" t="n">
+        <v>2.92521827380881</v>
+      </c>
+      <c r="I26" t="n">
+        <v>1.122242023082145</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0.9663526816021725</v>
+      </c>
+      <c r="K26" t="n">
+        <v>-2.378633887179403</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0.6715657249196414</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0.2319404500084588</v>
+      </c>
+      <c r="N26" t="n">
+        <v>-0.7325238908283813</v>
+      </c>
+      <c r="O26" t="n">
+        <v>-0.8110274889439115</v>
+      </c>
+      <c r="P26" t="n">
+        <v>-0.8079211832087353</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2022Q2</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>-0.05706656655871245</v>
+      </c>
+      <c r="C27" t="n">
+        <v>-0.03808271828893064</v>
+      </c>
+      <c r="D27" t="n">
+        <v>-0.04421044654061603</v>
+      </c>
+      <c r="E27" t="n">
+        <v>-0.04836191131979351</v>
+      </c>
+      <c r="F27" t="n">
+        <v>6.938688196993537</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0.3760814801813507</v>
+      </c>
+      <c r="H27" t="n">
+        <v>4.346898488000489</v>
+      </c>
+      <c r="I27" t="n">
+        <v>1.142647376376593</v>
+      </c>
+      <c r="J27" t="n">
+        <v>1.003627726193047</v>
+      </c>
+      <c r="K27" t="n">
+        <v>-2.910969125598073</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0.6825833774483854</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0.2179142403388036</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0.8206606923052473</v>
+      </c>
+      <c r="O27" t="n">
+        <v>1.574713867348748</v>
+      </c>
+      <c r="P27" t="n">
+        <v>1.368315026424379</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2022Q3</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>-0.05368286541596445</v>
+      </c>
+      <c r="C28" t="n">
+        <v>-0.02620705822747653</v>
+      </c>
+      <c r="D28" t="n">
+        <v>-0.03097793142196359</v>
+      </c>
+      <c r="E28" t="n">
+        <v>-0.05419517884720446</v>
+      </c>
+      <c r="F28" t="n">
+        <v>10.48866296807011</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0.5756100309719755</v>
+      </c>
+      <c r="H28" t="n">
+        <v>5.803522037935103</v>
+      </c>
+      <c r="I28" t="n">
+        <v>1.072404905100367</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0.9306803093025072</v>
+      </c>
+      <c r="K28" t="n">
+        <v>-1.671705947240569</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0.6917713554881696</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0.2340697650432164</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0.5498007666561662</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0.06651312610086269</v>
+      </c>
+      <c r="P28" t="n">
+        <v>0.08593388268709257</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2023年报</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>-0.01885844145012161</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0.0007738973787585994</v>
+      </c>
+      <c r="D29" t="n">
+        <v>-0.001596117781624558</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.01095195226037299</v>
+      </c>
+      <c r="F29" t="n">
+        <v>11.94881669529749</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0.9437187854104849</v>
+      </c>
+      <c r="H29" t="n">
+        <v>11.40184204506914</v>
+      </c>
+      <c r="I29" t="n">
+        <v>1.076558240280838</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0.8759756507450424</v>
+      </c>
+      <c r="K29" t="n">
+        <v>1.120044048403951</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0.6900821144470105</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0.3281584124540244</v>
+      </c>
+      <c r="N29" t="n">
+        <v>0.631613084047544</v>
+      </c>
+      <c r="O29" t="n">
+        <v>-1.048181717991101</v>
+      </c>
+      <c r="P29" t="n">
+        <v>-0.9159321963527514</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2023Q1</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>4.407706486697638e-05</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0.01637789048221216</v>
+      </c>
+      <c r="D30" t="n">
+        <v>0.01251282606940502</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.01095829907596624</v>
+      </c>
+      <c r="F30" t="n">
+        <v>2.29596563493177</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0.2229906603451953</v>
+      </c>
+      <c r="H30" t="n">
+        <v>2.830106037860709</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0.9643608763153355</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0.7799896498188719</v>
+      </c>
+      <c r="K30" t="n">
+        <v>2.845515937182207</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0.7152090567855638</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0.2631526124570947</v>
+      </c>
+      <c r="N30" t="n">
+        <v>-0.7603812391964202</v>
+      </c>
+      <c r="O30" t="n">
+        <v>4.071020951407783</v>
+      </c>
+      <c r="P30" t="n">
+        <v>-2.878500391023667</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2023Q2</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>-0.001859766923241857</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0.007757405350331945</v>
+      </c>
+      <c r="D31" t="n">
+        <v>0.005594381489111584</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.01151286544436202</v>
+      </c>
+      <c r="F31" t="n">
+        <v>4.472787534086419</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0.4523025336372368</v>
+      </c>
+      <c r="H31" t="n">
+        <v>4.636124405146115</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0.9183181756481608</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0.7126035021039772</v>
+      </c>
+      <c r="K31" t="n">
+        <v>2.058170222564178</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0.7035686641952174</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0.2145883407341019</v>
+      </c>
+      <c r="N31" t="n">
+        <v>1.07727995303312</v>
+      </c>
+      <c r="O31" t="n">
+        <v>-0.01609412767181606</v>
+      </c>
+      <c r="P31" t="n">
+        <v>-0.07126523996320155</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2023Q3</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>-0.01031070620572794</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0.00587742622171874</v>
+      </c>
+      <c r="D32" t="n">
+        <v>0.00282581917567877</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.01392903885422189</v>
+      </c>
+      <c r="F32" t="n">
+        <v>6.896990604801771</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0.6764795947672703</v>
+      </c>
+      <c r="H32" t="n">
+        <v>6.638237338553815</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0.927566424153072</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0.7623794109163168</v>
+      </c>
+      <c r="K32" t="n">
+        <v>1.853067614526215</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0.7139508536156581</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0.2595812009219831</v>
+      </c>
+      <c r="N32" t="n">
+        <v>0.5164261918602329</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0.1489257890795981</v>
+      </c>
+      <c r="P32" t="n">
+        <v>-0.2340268142599117</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2024年报</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>-0.0236835477023305</v>
+      </c>
+      <c r="C33" t="n">
+        <v>-0.04484566776716211</v>
+      </c>
+      <c r="D33" t="n">
+        <v>-0.04733407423261553</v>
+      </c>
+      <c r="E33" t="n">
+        <v>-0.1451244530039043</v>
+      </c>
+      <c r="F33" t="n">
+        <v>10.60598906862485</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0.8400078151236101</v>
+      </c>
+      <c r="H33" t="n">
+        <v>10.13253743071334</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0.9128127369219106</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0.7814549889573787</v>
+      </c>
+      <c r="K33" t="n">
+        <v>-7.395128784682382</v>
+      </c>
+      <c r="L33" t="n">
+        <v>0.7467655508241479</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0.2700841466147796</v>
+      </c>
+      <c r="N33" t="n">
+        <v>0.2415731889035992</v>
+      </c>
+      <c r="O33" t="n">
+        <v>-10.47339475439719</v>
+      </c>
+      <c r="P33" t="n">
+        <v>-21.79705523785744</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2024Q1</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>-0.0009973890006886865</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0.007549568130327834</v>
+      </c>
+      <c r="D34" t="n">
+        <v>0.005909209411136924</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.008527845783113051</v>
+      </c>
+      <c r="F34" t="n">
+        <v>2.895475976233149</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0.2313205558055011</v>
+      </c>
+      <c r="H34" t="n">
+        <v>2.826545077769414</v>
+      </c>
+      <c r="I34" t="n">
+        <v>1.002909039307507</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0.8323400028380872</v>
+      </c>
+      <c r="K34" t="n">
+        <v>2.406255762856459</v>
+      </c>
+      <c r="L34" t="n">
+        <v>0.6956413758847635</v>
+      </c>
+      <c r="M34" t="n">
+        <v>0.2723415704292396</v>
+      </c>
+      <c r="N34" t="n">
+        <v>-0.7325191295314732</v>
+      </c>
+      <c r="O34" t="n">
+        <v>-1.045029211420065</v>
+      </c>
+      <c r="P34" t="n">
+        <v>-1.033392445140136</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2024Q2</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>-0.002856500693857233</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0.01125981787428988</v>
+      </c>
+      <c r="D35" t="n">
+        <v>0.009323225222315311</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.02240310622952041</v>
+      </c>
+      <c r="F35" t="n">
+        <v>5.163455183855917</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0.4405377019598717</v>
+      </c>
+      <c r="H35" t="n">
+        <v>4.669545100032887</v>
+      </c>
+      <c r="I35" t="n">
+        <v>1.013930885529158</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0.8442764578833694</v>
+      </c>
+      <c r="K35" t="n">
+        <v>3.05787439171992</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0.6961258579343422</v>
+      </c>
+      <c r="M35" t="n">
+        <v>0.2871495906722897</v>
+      </c>
+      <c r="N35" t="n">
+        <v>0.8905837343189937</v>
+      </c>
+      <c r="O35" t="n">
+        <v>1.819714738252494</v>
+      </c>
+      <c r="P35" t="n">
+        <v>1.982858912307633</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2024Q3</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>-0.0114260679695406</v>
+      </c>
+      <c r="C36" t="n">
+        <v>0.01705345839451109</v>
+      </c>
+      <c r="D36" t="n">
+        <v>0.01463897033305951</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.04593775852292769</v>
+      </c>
+      <c r="F36" t="n">
+        <v>7.86335878614122</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0.6528282508594653</v>
+      </c>
+      <c r="H36" t="n">
+        <v>7.909129690483792</v>
+      </c>
+      <c r="I36" t="n">
+        <v>1.011897241524532</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0.8477223275075455</v>
+      </c>
+      <c r="K36" t="n">
+        <v>4.231058977914664</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0.7042191911560027</v>
+      </c>
+      <c r="M36" t="n">
+        <v>0.2637292718813377</v>
+      </c>
+      <c r="N36" t="n">
+        <v>0.5121741849484862</v>
+      </c>
+      <c r="O36" t="n">
+        <v>1.290250147576129</v>
+      </c>
+      <c r="P36" t="n">
+        <v>1.374357854071229</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2025年报</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>-0.03500318864222085</v>
+      </c>
+      <c r="C37" t="n">
+        <v>-0.03626124386436052</v>
+      </c>
+      <c r="D37" t="n">
+        <v>-0.03811700422180582</v>
+      </c>
+      <c r="E37" t="n">
+        <v>-0.1453265771328582</v>
+      </c>
+      <c r="F37" t="n">
+        <v>13.29717187997236</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0.9187285439253169</v>
+      </c>
+      <c r="H37" t="n">
+        <v>13.37623279653188</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0.8025869859918663</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0.709528920018075</v>
+      </c>
+      <c r="K37" t="n">
+        <v>-6.479395683258311</v>
+      </c>
+      <c r="L37" t="n">
+        <v>0.7907036163522012</v>
+      </c>
+      <c r="M37" t="n">
+        <v>0.33687106918239</v>
+      </c>
+      <c r="N37" t="n">
+        <v>0.4430775427438474</v>
+      </c>
+      <c r="O37" t="n">
+        <v>-4.068455997726494</v>
+      </c>
+      <c r="P37" t="n">
+        <v>-4.757490556896586</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2025Q1</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>-0.01379075990940448</v>
+      </c>
+      <c r="C38" t="n">
+        <v>-0.01781624372372356</v>
+      </c>
+      <c r="D38" t="n">
+        <v>-0.02453821865987186</v>
+      </c>
+      <c r="E38" t="n">
+        <v>-0.0213594120655141</v>
+      </c>
+      <c r="F38" t="n">
+        <v>2.994586497203134</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0.1976501192552484</v>
+      </c>
+      <c r="H38" t="n">
+        <v>2.752282073437237</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0.8932782626074213</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0.7583438811538206</v>
+      </c>
+      <c r="K38" t="n">
+        <v>-2.093077922293211</v>
+      </c>
+      <c r="L38" t="n">
+        <v>0.7466144862715866</v>
+      </c>
+      <c r="M38" t="n">
+        <v>0.2485401913281153</v>
+      </c>
+      <c r="N38" t="n">
+        <v>-0.7891183550478887</v>
+      </c>
+      <c r="O38" t="n">
+        <v>-0.8963874819799205</v>
+      </c>
+      <c r="P38" t="n">
+        <v>-0.8642427436039669</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2025Q2</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>-0.03757194727085533</v>
+      </c>
+      <c r="C39" t="n">
+        <v>-0.04195433547041944</v>
+      </c>
+      <c r="D39" t="n">
+        <v>-0.04413132256870946</v>
+      </c>
+      <c r="E39" t="n">
+        <v>-0.07096200592442954</v>
+      </c>
+      <c r="F39" t="n">
+        <v>5.266035729778477</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0.4075040045259269</v>
+      </c>
+      <c r="H39" t="n">
+        <v>4.724808785605857</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0.8089561110927644</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0.6642449060466959</v>
+      </c>
+      <c r="K39" t="n">
+        <v>-6.071996912714862</v>
+      </c>
+      <c r="L39" t="n">
+        <v>0.7525629775485307</v>
+      </c>
+      <c r="M39" t="n">
+        <v>0.2370995013162682</v>
+      </c>
+      <c r="N39" t="n">
+        <v>0.9753237448813443</v>
+      </c>
+      <c r="O39" t="n">
+        <v>3.651563839188251</v>
+      </c>
+      <c r="P39" t="n">
+        <v>2.552566328115237</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2025Q3</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>-0.04682193137585089</v>
+      </c>
+      <c r="C40" t="n">
+        <v>-0.04722499530075613</v>
+      </c>
+      <c r="D40" t="n">
+        <v>-0.04944822382726176</v>
+      </c>
+      <c r="E40" t="n">
+        <v>-0.139793507356109</v>
+      </c>
+      <c r="F40" t="n">
+        <v>8.075580437836082</v>
+      </c>
+      <c r="G40" t="n">
+        <v>0.6506689878233013</v>
+      </c>
+      <c r="H40" t="n">
+        <v>6.512591949001161</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0.8033077377436503</v>
+      </c>
+      <c r="J40" t="n">
+        <v>0.6696614542854478</v>
+      </c>
+      <c r="K40" t="n">
+        <v>-7.560014096992385</v>
+      </c>
+      <c r="L40" t="n">
+        <v>0.7744794802067548</v>
+      </c>
+      <c r="M40" t="n">
+        <v>0.2492267452722479</v>
+      </c>
+      <c r="N40" t="n">
+        <v>0.5946846707402471</v>
+      </c>
+      <c r="O40" t="n">
+        <v>0.7950224985685634</v>
+      </c>
+      <c r="P40" t="n">
+        <v>0.7868108169633063</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/600418_江淮汽车_财务数据.xlsx
+++ b/data/600418_江淮汽车_财务数据.xlsx
@@ -39731,7 +39731,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P40"/>
+  <dimension ref="A1:S40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39810,6 +39810,21 @@
           <t>净利润增长率</t>
         </is>
       </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>有息负债率</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>经营现金流/营收</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>权益乘数</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -39862,6 +39877,15 @@
       <c r="P2" t="n">
         <v>-0.77189706996788</v>
       </c>
+      <c r="Q2" t="n">
+        <v>0.09466109665142933</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0.1164772455535403</v>
+      </c>
+      <c r="S2" t="n">
+        <v>5.278342184253059</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -39914,6 +39938,15 @@
       <c r="P3" t="n">
         <v>1.15902560863391</v>
       </c>
+      <c r="Q3" t="n">
+        <v>0.1236874613959234</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0.0540350425204021</v>
+      </c>
+      <c r="S3" t="n">
+        <v>5.209975864843122</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -39966,6 +39999,15 @@
       <c r="P4" t="n">
         <v>0.4052435990816581</v>
       </c>
+      <c r="Q4" t="n">
+        <v>0.1127429049388239</v>
+      </c>
+      <c r="R4" t="n">
+        <v>-0.01209025302326347</v>
+      </c>
+      <c r="S4" t="n">
+        <v>3.82308321558712</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -40018,6 +40060,15 @@
       <c r="P5" t="n">
         <v>-0.7176508416395322</v>
       </c>
+      <c r="Q5" t="n">
+        <v>0.15504381037969</v>
+      </c>
+      <c r="R5" t="n">
+        <v>-0.1355751059568203</v>
+      </c>
+      <c r="S5" t="n">
+        <v>3.209084354722422</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -40070,6 +40121,15 @@
       <c r="P6" t="n">
         <v>0.08013460481801249</v>
       </c>
+      <c r="Q6" t="n">
+        <v>0.1162925921618793</v>
+      </c>
+      <c r="R6" t="n">
+        <v>-0.1837551964720302</v>
+      </c>
+      <c r="S6" t="n">
+        <v>3.665648312611013</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -40122,6 +40182,15 @@
       <c r="P7" t="n">
         <v>0.2136826209218605</v>
       </c>
+      <c r="Q7" t="n">
+        <v>0.1368863196855961</v>
+      </c>
+      <c r="R7" t="n">
+        <v>-0.1535153814559293</v>
+      </c>
+      <c r="S7" t="n">
+        <v>3.488141002393559</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -40174,6 +40243,15 @@
       <c r="P8" t="n">
         <v>-0.5980762286164212</v>
       </c>
+      <c r="Q8" t="n">
+        <v>0.1552797661908594</v>
+      </c>
+      <c r="R8" t="n">
+        <v>-0.1428187442367643</v>
+      </c>
+      <c r="S8" t="n">
+        <v>3.458180752892925</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -40226,6 +40304,15 @@
       <c r="P9" t="n">
         <v>-12.36023496941143</v>
       </c>
+      <c r="Q9" t="n">
+        <v>0.2179735534405795</v>
+      </c>
+      <c r="R9" t="n">
+        <v>-0.06895347385559818</v>
+      </c>
+      <c r="S9" t="n">
+        <v>3.694150591163659</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -40278,6 +40365,15 @@
       <c r="P10" t="n">
         <v>-1.102134696546141</v>
       </c>
+      <c r="Q10" t="n">
+        <v>0.2182513618977707</v>
+      </c>
+      <c r="R10" t="n">
+        <v>-0.1949651578628451</v>
+      </c>
+      <c r="S10" t="n">
+        <v>3.67525736599219</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -40330,6 +40426,15 @@
       <c r="P11" t="n">
         <v>-0.6707372114904533</v>
       </c>
+      <c r="Q11" t="n">
+        <v>0.2311963863909494</v>
+      </c>
+      <c r="R11" t="n">
+        <v>-0.1106744957861639</v>
+      </c>
+      <c r="S11" t="n">
+        <v>3.497753297579359</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -40382,6 +40487,15 @@
       <c r="P12" t="n">
         <v>-4.474444793136728</v>
       </c>
+      <c r="Q12" t="n">
+        <v>0.2163714393907519</v>
+      </c>
+      <c r="R12" t="n">
+        <v>-0.1140895305650436</v>
+      </c>
+      <c r="S12" t="n">
+        <v>3.47293051800979</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -40434,6 +40548,15 @@
       <c r="P13" t="n">
         <v>-2.034873828792833</v>
       </c>
+      <c r="Q13" t="n">
+        <v>0.2369855204651693</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0.004779422902104057</v>
+      </c>
+      <c r="S13" t="n">
+        <v>3.385963557751698</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -40486,6 +40609,15 @@
       <c r="P14" t="n">
         <v>-0.5539542037653891</v>
       </c>
+      <c r="Q14" t="n">
+        <v>0.2143146714233591</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0.001951395914807243</v>
+      </c>
+      <c r="S14" t="n">
+        <v>3.816648615194182</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -40538,6 +40670,15 @@
       <c r="P15" t="n">
         <v>1.076631938075495</v>
       </c>
+      <c r="Q15" t="n">
+        <v>0.2169115418039247</v>
+      </c>
+      <c r="R15" t="n">
+        <v>-0.03959244589895856</v>
+      </c>
+      <c r="S15" t="n">
+        <v>3.81004081004081</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -40590,6 +40731,15 @@
       <c r="P16" t="n">
         <v>0.6058677025902812</v>
       </c>
+      <c r="Q16" t="n">
+        <v>0.2216654635016349</v>
+      </c>
+      <c r="R16" t="n">
+        <v>-0.06271014229711529</v>
+      </c>
+      <c r="S16" t="n">
+        <v>3.625432992071434</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -40642,6 +40792,15 @@
       <c r="P17" t="n">
         <v>-0.02361786164455171</v>
       </c>
+      <c r="Q17" t="n">
+        <v>0.2277227722772277</v>
+      </c>
+      <c r="R17" t="n">
+        <v>-0.03107579101915043</v>
+      </c>
+      <c r="S17" t="n">
+        <v>3.226614571362905</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -40694,6 +40853,15 @@
       <c r="P18" t="n">
         <v>-2.583412104665093</v>
       </c>
+      <c r="Q18" t="n">
+        <v>0.2457449391818804</v>
+      </c>
+      <c r="R18" t="n">
+        <v>-0.2515568399374462</v>
+      </c>
+      <c r="S18" t="n">
+        <v>3.59515873015873</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -40746,6 +40914,15 @@
       <c r="P19" t="n">
         <v>-0.5380884453449956</v>
       </c>
+      <c r="Q19" t="n">
+        <v>0.2490399720719148</v>
+      </c>
+      <c r="R19" t="n">
+        <v>-0.1106037319485252</v>
+      </c>
+      <c r="S19" t="n">
+        <v>3.588755774802286</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -40798,6 +40975,15 @@
       <c r="P20" t="n">
         <v>-2.285981800910681</v>
       </c>
+      <c r="Q20" t="n">
+        <v>0.2444802508383051</v>
+      </c>
+      <c r="R20" t="n">
+        <v>-0.05693023028339056</v>
+      </c>
+      <c r="S20" t="n">
+        <v>3.545040524893863</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -40850,6 +41036,15 @@
       <c r="P21" t="n">
         <v>-0.944426022080023</v>
       </c>
+      <c r="Q21" t="n">
+        <v>0.2283157213715765</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0.04289601984859508</v>
+      </c>
+      <c r="S21" t="n">
+        <v>3.042251673008792</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -40902,6 +41097,15 @@
       <c r="P22" t="n">
         <v>12.47853462822034</v>
       </c>
+      <c r="Q22" t="n">
+        <v>0.232635595185396</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0.02970806058570791</v>
+      </c>
+      <c r="S22" t="n">
+        <v>3.582735442942376</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -40954,6 +41158,15 @@
       <c r="P23" t="n">
         <v>1.470516559179919</v>
       </c>
+      <c r="Q23" t="n">
+        <v>0.2384422003493971</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0.03176662203624711</v>
+      </c>
+      <c r="S23" t="n">
+        <v>3.472773009766203</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -41006,6 +41219,15 @@
       <c r="P24" t="n">
         <v>-0.6902711154763287</v>
       </c>
+      <c r="Q24" t="n">
+        <v>0.243730407523511</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0.01682616448506084</v>
+      </c>
+      <c r="S24" t="n">
+        <v>3.374641076016322</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -41058,6 +41280,15 @@
       <c r="P25" t="n">
         <v>-13.8423048658334</v>
       </c>
+      <c r="Q25" t="n">
+        <v>0.2277255060212816</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0.04195132704248326</v>
+      </c>
+      <c r="S25" t="n">
+        <v>3.451073810745437</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -41110,6 +41341,15 @@
       <c r="P26" t="n">
         <v>-0.8079211832087353</v>
       </c>
+      <c r="Q26" t="n">
+        <v>0.2174335983759093</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0.1193469819179533</v>
+      </c>
+      <c r="S26" t="n">
+        <v>3.161596576853647</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -41162,6 +41402,15 @@
       <c r="P27" t="n">
         <v>1.368315026424379</v>
       </c>
+      <c r="Q27" t="n">
+        <v>0.2479195341450503</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0.0346044232555772</v>
+      </c>
+      <c r="S27" t="n">
+        <v>3.259819148201836</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -41214,6 +41463,15 @@
       <c r="P28" t="n">
         <v>0.08593388268709257</v>
       </c>
+      <c r="Q28" t="n">
+        <v>0.2402582668069394</v>
+      </c>
+      <c r="R28" t="n">
+        <v>0.07235822868508374</v>
+      </c>
+      <c r="S28" t="n">
+        <v>3.358528474435361</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -41266,6 +41524,15 @@
       <c r="P29" t="n">
         <v>-0.9159321963527514</v>
       </c>
+      <c r="Q29" t="n">
+        <v>0.1603593747327004</v>
+      </c>
+      <c r="R29" t="n">
+        <v>0.07556681718200686</v>
+      </c>
+      <c r="S29" t="n">
+        <v>3.533625510049871</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -41318,6 +41585,15 @@
       <c r="P30" t="n">
         <v>-2.878500391023667</v>
       </c>
+      <c r="Q30" t="n">
+        <v>0.1922158212730083</v>
+      </c>
+      <c r="R30" t="n">
+        <v>0.1675248216341771</v>
+      </c>
+      <c r="S30" t="n">
+        <v>3.615836841341268</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -41370,6 +41646,15 @@
       <c r="P31" t="n">
         <v>-0.07126523996320155</v>
       </c>
+      <c r="Q31" t="n">
+        <v>0.1829144090927608</v>
+      </c>
+      <c r="R31" t="n">
+        <v>0.02601780088647762</v>
+      </c>
+      <c r="S31" t="n">
+        <v>3.724321043847671</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -41422,6 +41707,15 @@
       <c r="P32" t="n">
         <v>-0.2340268142599117</v>
       </c>
+      <c r="Q32" t="n">
+        <v>0.1625385787396961</v>
+      </c>
+      <c r="R32" t="n">
+        <v>0.1097832280046857</v>
+      </c>
+      <c r="S32" t="n">
+        <v>3.870123979437557</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -41474,6 +41768,15 @@
       <c r="P33" t="n">
         <v>-21.79705523785744</v>
       </c>
+      <c r="Q33" t="n">
+        <v>0.148000244493796</v>
+      </c>
+      <c r="R33" t="n">
+        <v>0.06437000101752514</v>
+      </c>
+      <c r="S33" t="n">
+        <v>4.320510563380282</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -41526,6 +41829,15 @@
       <c r="P34" t="n">
         <v>-1.033392445140136</v>
       </c>
+      <c r="Q34" t="n">
+        <v>0.1533185520923879</v>
+      </c>
+      <c r="R34" t="n">
+        <v>-0.1088307797296806</v>
+      </c>
+      <c r="S34" t="n">
+        <v>3.610940886331365</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -41578,6 +41890,15 @@
       <c r="P35" t="n">
         <v>1.982858912307633</v>
       </c>
+      <c r="Q35" t="n">
+        <v>0.1403051331348714</v>
+      </c>
+      <c r="R35" t="n">
+        <v>0.002845374341680367</v>
+      </c>
+      <c r="S35" t="n">
+        <v>3.589758812615956</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -41630,6 +41951,15 @@
       <c r="P36" t="n">
         <v>1.374357854071229</v>
       </c>
+      <c r="Q36" t="n">
+        <v>0.1390225474211635</v>
+      </c>
+      <c r="R36" t="n">
+        <v>0.06632309461420774</v>
+      </c>
+      <c r="S36" t="n">
+        <v>3.660141183319991</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -41682,6 +42012,15 @@
       <c r="P37" t="n">
         <v>-4.757490556896586</v>
       </c>
+      <c r="Q37" t="n">
+        <v>0.1211084905660377</v>
+      </c>
+      <c r="R37" t="n">
+        <v>0.07304889386964235</v>
+      </c>
+      <c r="S37" t="n">
+        <v>5.25077399380805</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -41734,6 +42073,15 @@
       <c r="P38" t="n">
         <v>-0.8642427436039669</v>
       </c>
+      <c r="Q38" t="n">
+        <v>0.1447798898413882</v>
+      </c>
+      <c r="R38" t="n">
+        <v>-0.1320290083053019</v>
+      </c>
+      <c r="S38" t="n">
+        <v>4.31543204360647</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -41786,6 +42134,15 @@
       <c r="P39" t="n">
         <v>2.552566328115237</v>
       </c>
+      <c r="Q39" t="n">
+        <v>0.1455814053035978</v>
+      </c>
+      <c r="R39" t="n">
+        <v>-0.1625524589460413</v>
+      </c>
+      <c r="S39" t="n">
+        <v>4.411992445703494</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -41837,6 +42194,15 @@
       </c>
       <c r="P40" t="n">
         <v>0.7868108169633063</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>0.1400784671911652</v>
+      </c>
+      <c r="R40" t="n">
+        <v>-0.079292734374189</v>
+      </c>
+      <c r="S40" t="n">
+        <v>4.851747406586766</v>
       </c>
     </row>
   </sheetData>
